--- a/COI_Template.xlsx
+++ b/COI_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr date1904="1" filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{E81346F3-BC96-4226-9317-ED0D14BD1A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38A32473-5461-4B0A-A816-B2911B4CD738}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{E81346F3-BC96-4226-9317-ED0D14BD1A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D24524B-9470-4213-BC43-DBCD1851BDF6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Node_Type" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="Edge" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Edge!$A$1:$F$913</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Edge!$A$1:$F$914</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Node!$A$1:$F$473</definedName>
   </definedNames>
   <calcPr calcId="191028" calcOnSave="0"/>
@@ -18200,7 +18200,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F906" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="A1:F914" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <legacyDrawing r:id="rId1"/>

--- a/COI_Template.xlsx
+++ b/COI_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr date1904="1" filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="113" documentId="8_{E81346F3-BC96-4226-9317-ED0D14BD1A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5123D4F0-909E-40E1-A99A-054752360D6A}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{E81346F3-BC96-4226-9317-ED0D14BD1A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FE36D97-15C0-4CA0-803A-A04AC68EF748}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Node_Type" sheetId="1" r:id="rId1"/>
@@ -204,7 +204,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3839" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="566">
   <si>
     <t>Color</t>
   </si>
@@ -1896,6 +1896,13 @@
   </si>
   <si>
     <t>Arrows</t>
+  </si>
+  <si>
+    <t>Media: Obituary
+Who is Johannes von Baumbach, the world's youngest billionaire? What we know about him| Business News</t>
+  </si>
+  <si>
+    <t>Media: Woolworths' South Africa CEO Bagattini to retire in September - FashionNetwork Area Hong Kong</t>
   </si>
 </sst>
 </file>
@@ -16475,6 +16482,9 @@
       <c r="C883" t="s">
         <v>513</v>
       </c>
+      <c r="D883" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="884" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
@@ -16522,13 +16532,16 @@
       <c r="C887" t="s">
         <v>513</v>
       </c>
+      <c r="D887" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="888" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
+        <v>33</v>
+      </c>
+      <c r="B888" t="s">
         <v>31</v>
-      </c>
-      <c r="B888" t="s">
-        <v>33</v>
       </c>
       <c r="C888" t="s">
         <v>519</v>
@@ -16536,10 +16549,10 @@
     </row>
     <row r="889" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
+        <v>34</v>
+      </c>
+      <c r="B889" t="s">
         <v>31</v>
-      </c>
-      <c r="B889" t="s">
-        <v>34</v>
       </c>
       <c r="C889" t="s">
         <v>520</v>
@@ -16547,10 +16560,10 @@
     </row>
     <row r="890" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
+        <v>35</v>
+      </c>
+      <c r="B890" t="s">
         <v>31</v>
-      </c>
-      <c r="B890" t="s">
-        <v>35</v>
       </c>
       <c r="C890" t="s">
         <v>519</v>
@@ -16558,10 +16571,10 @@
     </row>
     <row r="891" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
+        <v>36</v>
+      </c>
+      <c r="B891" t="s">
         <v>31</v>
-      </c>
-      <c r="B891" t="s">
-        <v>36</v>
       </c>
       <c r="C891" t="s">
         <v>519</v>
@@ -16937,25 +16950,25 @@
           <x14:formula1>
             <xm:f>Node!A$2:A$9986</xm:f>
           </x14:formula1>
-          <xm:sqref>A913:B913 A907:B908 A858 A2:A468 A904:A906 A896 A894 B906 A916:A9987</xm:sqref>
+          <xm:sqref>A913:B913 A916:A9987 B906 A894 A896 A904:A906 A907:B908 A2:A468 A858</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showErrorMessage="1" error="Please select value from column &quot;Name&quot; in sheet &quot;Node&quot;" xr:uid="{38A5A17A-6382-416D-9A8B-CADE8BD221DB}">
           <x14:formula1>
             <xm:f>Node!A$2:A$9986</xm:f>
           </x14:formula1>
-          <xm:sqref>B915:B9987 B903:B905 B2:B468 B873 B875</xm:sqref>
+          <xm:sqref>B915:B9987 B903:B905 B875 B873 B2:B468</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" showErrorMessage="1" error="Please select value from column &quot;Name&quot; in sheet &quot;Edge_Type&quot;" xr:uid="{D66E5D5B-6677-47B1-99CD-E5ED37794854}">
+          <x14:formula1>
+            <xm:f>Edge_Type!A$2:A$9987</xm:f>
+          </x14:formula1>
+          <xm:sqref>C878 C852:C858 C860:C863 C849 C2:C468 C819:C847 C870:C875 C880:C881 C865:C868 C888:C9987</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showErrorMessage="1" error="Please select value from column &quot;Name&quot; in sheet &quot;Node&quot;" xr:uid="{0C3294F7-C558-4DB9-8551-AB1F5A0CB7B6}">
           <x14:formula1>
             <xm:f>Node!XFC$2:XFD$9986</xm:f>
           </x14:formula1>
           <xm:sqref>A872</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" showErrorMessage="1" error="Please select value from column &quot;Name&quot; in sheet &quot;Edge_Type&quot;" xr:uid="{D66E5D5B-6677-47B1-99CD-E5ED37794854}">
-          <x14:formula1>
-            <xm:f>Edge_Type!A$2:A$9987</xm:f>
-          </x14:formula1>
-          <xm:sqref>C865:C868 C880:C881 C870:C875 C819:C847 C2:C468 C849 C860:C863 C852:C858 C878 C888:C9987</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/COI_Template.xlsx
+++ b/COI_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr date1904="1" filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="130" documentId="8_{E81346F3-BC96-4226-9317-ED0D14BD1A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FE36D97-15C0-4CA0-803A-A04AC68EF748}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="8_{E81346F3-BC96-4226-9317-ED0D14BD1A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74CFC16A-0D73-4EC2-B3A4-AFB228272032}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Node_Type" sheetId="1" r:id="rId1"/>
@@ -204,7 +204,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3840" uniqueCount="566">
   <si>
     <t>Color</t>
   </si>
@@ -1898,11 +1898,12 @@
     <t>Arrows</t>
   </si>
   <si>
-    <t>Media: Obituary
+    <t>Media: Woolworths' South Africa CEO Bagattini to retire in September - FashionNetwork Area Hong Kong</t>
+  </si>
+  <si>
+    <t>Media - Hubertus von Baumbach​ Succession
+Media: Obituary
 Who is Johannes von Baumbach, the world's youngest billionaire? What we know about him| Business News</t>
-  </si>
-  <si>
-    <t>Media: Woolworths' South Africa CEO Bagattini to retire in September - FashionNetwork Area Hong Kong</t>
   </si>
 </sst>
 </file>
@@ -2603,9 +2604,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>32</v>
+    <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>565</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -16483,7 +16484,7 @@
         <v>513</v>
       </c>
       <c r="D883" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="884" spans="1:4" x14ac:dyDescent="0.3">
@@ -16531,9 +16532,6 @@
       </c>
       <c r="C887" t="s">
         <v>513</v>
-      </c>
-      <c r="D887" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="888" spans="1:4" x14ac:dyDescent="0.3">

--- a/COI_Template.xlsx
+++ b/COI_Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr date1904="1" filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="133" documentId="8_{E81346F3-BC96-4226-9317-ED0D14BD1A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74CFC16A-0D73-4EC2-B3A4-AFB228272032}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Node_Type" sheetId="1" r:id="rId1"/>
